--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -53554,13 +53554,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -53713,10 +53713,10 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -32417,7 +32417,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -39411,7 +39411,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -45764,13 +45764,13 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -45923,10 +45923,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -53122,12 +53122,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -53152,104 +53152,102 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.00367281181951979</v>
+        <v>0</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -53281,12 +53279,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -53311,38 +53309,41 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
         </is>
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X265" t="inlineStr">
         <is>
-          <t>Hepatitis B (newly acquired)</t>
+          <t>Acute Viral Hepatitis B</t>
         </is>
       </c>
       <c r="Y265" t="inlineStr">
@@ -53352,12 +53353,12 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
@@ -53367,7 +53368,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -53382,7 +53383,7 @@
       </c>
       <c r="AF265" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG265" t="inlineStr">
@@ -53402,12 +53403,12 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM265" t="inlineStr">
@@ -53420,70 +53421,70 @@
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr">
         <is>
-          <t>SER_AU_HEPATITIS_B_NEW</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
         </is>
       </c>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -53515,12 +53516,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -53560,7 +53561,7 @@
         <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -53569,7 +53570,7 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -53579,7 +53580,7 @@
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
@@ -53589,12 +53590,12 @@
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT266" t="n">
@@ -53602,47 +53603,47 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53674,12 +53675,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -53720,22 +53721,22 @@
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>Hepatitis B, acute</t>
+          <t>Hepatitis B (newly acquired)</t>
         </is>
       </c>
       <c r="Y267" t="inlineStr">
@@ -53745,7 +53746,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -53760,7 +53761,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -53775,7 +53776,7 @@
       </c>
       <c r="AF267" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG267" t="inlineStr">
@@ -53795,17 +53796,17 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Newly acquired hepatitis B, separate from unspecified hepatitis B.</t>
         </is>
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -53813,7 +53814,7 @@
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
@@ -53823,12 +53824,12 @@
       </c>
       <c r="AQ267" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT267" t="n">
@@ -53836,47 +53837,47 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53908,12 +53909,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -53947,13 +53948,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -53962,7 +53963,7 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -53982,12 +53983,12 @@
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -53995,47 +53996,47 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -54067,12 +54068,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -54106,29 +54107,29 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>Hepatitt B, akutt</t>
+          <t>Hepatitis B, acute</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr">
@@ -54153,7 +54154,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -54188,17 +54189,17 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -54216,12 +54217,12 @@
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -54229,47 +54230,1091 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV269" t="inlineStr">
+      <c r="AV270" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW269" t="inlineStr">
+      <c r="AW270" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX269" t="inlineStr">
+      <c r="AX270" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY269" t="inlineStr">
+      <c r="AY270" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ269" t="inlineStr">
+      <c r="AZ270" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA269" t="inlineStr">
+      <c r="BA270" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB269" t="inlineStr">
+      <c r="BB270" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC269" t="inlineStr">
+      <c r="BC270" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>Hepatitt B, akutt</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS acute category.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>6</v>
+      </c>
+      <c r="O272" t="n">
+        <v>6</v>
+      </c>
+      <c r="P272" t="n">
+        <v>6</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>6</v>
+      </c>
+      <c r="O273" t="n">
+        <v>6</v>
+      </c>
+      <c r="P273" t="n">
+        <v>6</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>4</v>
+      </c>
+      <c r="O274" t="n">
+        <v>4</v>
+      </c>
+      <c r="P274" t="n">
+        <v>4</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54306,7 +55351,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -54389,7 +55434,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -54399,7 +55444,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -54419,7 +55464,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -54451,7 +55496,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>774</v>
+        <v>784</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -53551,16 +53551,16 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -53708,13 +53708,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
@@ -55703,6 +55703,1051 @@
         </is>
       </c>
       <c r="BC276" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="n">
+        <v>1</v>
+      </c>
+      <c r="P277" t="n">
+        <v>1</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>1</v>
+      </c>
+      <c r="O278" t="n">
+        <v>1</v>
+      </c>
+      <c r="P278" t="n">
+        <v>1</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN278" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>12</v>
+      </c>
+      <c r="O279" t="n">
+        <v>12</v>
+      </c>
+      <c r="P279" t="n">
+        <v>12</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0.003438045759323263</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>12</v>
+      </c>
+      <c r="O280" t="n">
+        <v>12</v>
+      </c>
+      <c r="P280" t="n">
+        <v>12</v>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN280" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>7</v>
+      </c>
+      <c r="O281" t="n">
+        <v>7</v>
+      </c>
+      <c r="P281" t="n">
+        <v>7</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -55741,7 +56786,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -55824,7 +56869,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -55834,7 +56879,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
@@ -55854,7 +56899,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -55886,7 +56931,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>795</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16664,7 +16664,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21527,7 +21527,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -22572,7 +22572,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28238,7 +28238,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28480,7 +28480,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30570,7 +30570,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -31373,7 +31373,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -31615,7 +31615,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35232,7 +35232,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35474,7 +35474,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -36277,7 +36277,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -37322,7 +37322,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37564,7 +37564,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -38367,7 +38367,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
@@ -38609,7 +38609,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -39401,7 +39401,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -41822,7 +41822,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42226,7 +42226,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -43271,7 +43271,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -43513,7 +43513,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44316,7 +44316,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44558,7 +44558,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -45361,7 +45361,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -45603,7 +45603,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46395,7 +46395,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -48568,7 +48568,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -48972,7 +48972,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -49214,7 +49214,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -50017,7 +50017,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -50259,7 +50259,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -51062,7 +51062,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -51304,7 +51304,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -52107,7 +52107,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52349,7 +52349,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -53152,7 +53152,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -53394,7 +53394,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -54186,7 +54186,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -55376,7 +55376,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55618,7 +55618,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -56421,7 +56421,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -56663,7 +56663,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56748,6 +56748,1051 @@
         </is>
       </c>
       <c r="BC281" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>16</v>
+      </c>
+      <c r="O284" t="n">
+        <v>16</v>
+      </c>
+      <c r="P284" t="n">
+        <v>16</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0.004584061012431017</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>16</v>
+      </c>
+      <c r="O285" t="n">
+        <v>16</v>
+      </c>
+      <c r="P285" t="n">
+        <v>16</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN285" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>4</v>
+      </c>
+      <c r="O286" t="n">
+        <v>4</v>
+      </c>
+      <c r="P286" t="n">
+        <v>4</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -56786,7 +57831,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -56869,7 +57914,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -56879,7 +57924,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
@@ -56899,7 +57944,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -56931,7 +57976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>809</v>
+        <v>825</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -53945,13 +53945,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R268" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.01101843545855937</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -54104,10 +54104,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -54338,13 +54338,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O270" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R270" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -54497,10 +54497,10 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O271" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -57795,6 +57795,1444 @@
       <c r="BC286" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="n">
+        <v>1</v>
+      </c>
+      <c r="P287" t="n">
+        <v>1</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>1</v>
+      </c>
+      <c r="P288" t="n">
+        <v>1</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis B</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_B; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>16</v>
+      </c>
+      <c r="O289" t="n">
+        <v>16</v>
+      </c>
+      <c r="P289" t="n">
+        <v>16</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.004584061012431017</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>16</v>
+      </c>
+      <c r="O290" t="n">
+        <v>16</v>
+      </c>
+      <c r="P290" t="n">
+        <v>16</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN290" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="n">
+        <v>2</v>
+      </c>
+      <c r="P291" t="n">
+        <v>2</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_140</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_140</t>
+        </is>
+      </c>
+      <c r="AT292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_140</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_140</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN293" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_140</t>
+        </is>
+      </c>
+      <c r="AT293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -57831,7 +59269,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -57914,7 +59352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -57924,7 +59362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11">
@@ -57944,7 +59382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -57976,7 +59414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>825</v>
+        <v>846</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -34445,7 +34445,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -41439,7 +41439,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -48185,7 +48185,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -54982,7 +54982,7 @@
       </c>
       <c r="AM273" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN273" t="b">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -79858,6 +79858,657 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>9</v>
+      </c>
+      <c r="O400" t="n">
+        <v>9</v>
+      </c>
+      <c r="P400" t="n">
+        <v>9</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ400" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT400" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU400" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV400" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW400" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX400" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY400" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA400" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB400" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC400" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N401" t="n">
+        <v>9</v>
+      </c>
+      <c r="O401" t="n">
+        <v>9</v>
+      </c>
+      <c r="P401" t="n">
+        <v>9</v>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB401" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD401" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE401" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF401" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG401" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI401" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ401" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK401" t="inlineStr">
+        <is>
+          <t>Confirmed component of the NNDSS acute hepatitis B series.</t>
+        </is>
+      </c>
+      <c r="AM401" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN401" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO401" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP401" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ401" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR401" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS401" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT401" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU401" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV401" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW401" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX401" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY401" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA401" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB401" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC401" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>8</v>
+      </c>
+      <c r="O402" t="n">
+        <v>8</v>
+      </c>
+      <c r="P402" t="n">
+        <v>8</v>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>Hepatitis B, acute, Probable</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG402" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>Probable component retained separately; any confirmed-plus-probable sum requires an explicit disjoint-components rule.</t>
+        </is>
+      </c>
+      <c r="AM402" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN402" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO402" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP402" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ402" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR402" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS402" t="inlineStr">
+        <is>
+          <t>SER_US_ACUTE_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT402" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU402" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV402" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW402" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX402" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY402" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA402" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB402" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC402" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -79891,7 +80542,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -79974,7 +80625,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -79984,7 +80635,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -80004,7 +80655,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -80036,7 +80687,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>881</v>
+        <v>890</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -27097,13 +27097,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R185" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -2604,14 +2604,12 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="n">
         <v>0.0002865038132769385</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2624,22 +2622,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2901,14 +2889,12 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
       <c r="R17" t="n">
         <v>0.002865038132769385</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2921,22 +2907,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3198,14 +3174,12 @@
       <c r="O19" t="n">
         <v>17</v>
       </c>
+      <c r="P19" t="n">
+        <v>17</v>
+      </c>
       <c r="R19" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3218,22 +3192,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3495,14 +3459,12 @@
       <c r="O21" t="n">
         <v>14</v>
       </c>
+      <c r="P21" t="n">
+        <v>14</v>
+      </c>
       <c r="R21" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3515,22 +3477,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3792,14 +3744,12 @@
       <c r="O23" t="n">
         <v>19</v>
       </c>
+      <c r="P23" t="n">
+        <v>19</v>
+      </c>
       <c r="R23" t="n">
         <v>0.005443572452261832</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3812,22 +3762,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -5919,14 +5859,12 @@
       <c r="O38" t="n">
         <v>18</v>
       </c>
+      <c r="P38" t="n">
+        <v>18</v>
+      </c>
       <c r="R38" t="n">
         <v>0.005157068638984894</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5939,22 +5877,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6216,14 +6144,12 @@
       <c r="O40" t="n">
         <v>26</v>
       </c>
+      <c r="P40" t="n">
+        <v>26</v>
+      </c>
       <c r="R40" t="n">
         <v>0.007449099145200401</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6236,22 +6162,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6513,14 +6429,12 @@
       <c r="O42" t="n">
         <v>22</v>
       </c>
+      <c r="P42" t="n">
+        <v>22</v>
+      </c>
       <c r="R42" t="n">
         <v>0.006303083892092647</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6533,22 +6447,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6810,14 +6714,12 @@
       <c r="O44" t="n">
         <v>14</v>
       </c>
+      <c r="P44" t="n">
+        <v>14</v>
+      </c>
       <c r="R44" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6830,22 +6732,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -8955,14 +8847,12 @@
       <c r="O59" t="n">
         <v>17</v>
       </c>
+      <c r="P59" t="n">
+        <v>17</v>
+      </c>
       <c r="R59" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8975,22 +8865,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9252,14 +9132,12 @@
       <c r="O61" t="n">
         <v>22</v>
       </c>
+      <c r="P61" t="n">
+        <v>22</v>
+      </c>
       <c r="R61" t="n">
         <v>0.006303083892092647</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9272,22 +9150,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9549,14 +9417,12 @@
       <c r="O63" t="n">
         <v>13</v>
       </c>
+      <c r="P63" t="n">
+        <v>13</v>
+      </c>
       <c r="R63" t="n">
         <v>0.003724549572600201</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9569,22 +9435,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9846,14 +9702,12 @@
       <c r="O65" t="n">
         <v>14</v>
       </c>
+      <c r="P65" t="n">
+        <v>14</v>
+      </c>
       <c r="R65" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9866,22 +9720,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -11967,14 +11811,12 @@
       <c r="O80" t="n">
         <v>9</v>
       </c>
+      <c r="P80" t="n">
+        <v>9</v>
+      </c>
       <c r="R80" t="n">
         <v>0.002578534319492447</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11987,22 +11829,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12264,14 +12096,12 @@
       <c r="O82" t="n">
         <v>17</v>
       </c>
+      <c r="P82" t="n">
+        <v>17</v>
+      </c>
       <c r="R82" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12284,22 +12114,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12561,14 +12381,12 @@
       <c r="O84" t="n">
         <v>12</v>
       </c>
+      <c r="P84" t="n">
+        <v>12</v>
+      </c>
       <c r="R84" t="n">
         <v>0.003438045759323263</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12581,22 +12399,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12858,14 +12666,12 @@
       <c r="O86" t="n">
         <v>19</v>
       </c>
+      <c r="P86" t="n">
+        <v>19</v>
+      </c>
       <c r="R86" t="n">
         <v>0.005443572452261832</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12878,22 +12684,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -14988,14 +14784,12 @@
       <c r="O101" t="n">
         <v>20</v>
       </c>
+      <c r="P101" t="n">
+        <v>20</v>
+      </c>
       <c r="R101" t="n">
         <v>0.00573007626553877</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15008,22 +14802,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -15285,14 +15069,12 @@
       <c r="O103" t="n">
         <v>11</v>
       </c>
+      <c r="P103" t="n">
+        <v>11</v>
+      </c>
       <c r="R103" t="n">
         <v>0.003151541946046324</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15305,22 +15087,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15582,14 +15354,12 @@
       <c r="O105" t="n">
         <v>17</v>
       </c>
+      <c r="P105" t="n">
+        <v>17</v>
+      </c>
       <c r="R105" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15602,22 +15372,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15879,14 +15639,12 @@
       <c r="O107" t="n">
         <v>9</v>
       </c>
+      <c r="P107" t="n">
+        <v>9</v>
+      </c>
       <c r="R107" t="n">
         <v>0.002578534319492447</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15899,22 +15657,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -16176,14 +15924,12 @@
       <c r="O109" t="n">
         <v>10</v>
       </c>
+      <c r="P109" t="n">
+        <v>10</v>
+      </c>
       <c r="R109" t="n">
         <v>0.002865038132769385</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16196,22 +15942,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -18297,14 +18033,12 @@
       <c r="O124" t="n">
         <v>12</v>
       </c>
+      <c r="P124" t="n">
+        <v>12</v>
+      </c>
       <c r="R124" t="n">
         <v>0.003438045759323263</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18317,22 +18051,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18594,14 +18318,12 @@
       <c r="O126" t="n">
         <v>17</v>
       </c>
+      <c r="P126" t="n">
+        <v>17</v>
+      </c>
       <c r="R126" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18614,22 +18336,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18891,14 +18603,12 @@
       <c r="O128" t="n">
         <v>17</v>
       </c>
+      <c r="P128" t="n">
+        <v>17</v>
+      </c>
       <c r="R128" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18911,22 +18621,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -19188,14 +18888,12 @@
       <c r="O130" t="n">
         <v>17</v>
       </c>
+      <c r="P130" t="n">
+        <v>17</v>
+      </c>
       <c r="R130" t="n">
         <v>0.004870564825707955</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19208,22 +18906,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -21318,14 +21006,12 @@
       <c r="O145" t="n">
         <v>14</v>
       </c>
+      <c r="P145" t="n">
+        <v>14</v>
+      </c>
       <c r="R145" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21338,22 +21024,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21615,14 +21291,12 @@
       <c r="O147" t="n">
         <v>15</v>
       </c>
+      <c r="P147" t="n">
+        <v>15</v>
+      </c>
       <c r="R147" t="n">
         <v>0.004297557199154077</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21635,22 +21309,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21912,14 +21576,12 @@
       <c r="O149" t="n">
         <v>25</v>
       </c>
+      <c r="P149" t="n">
+        <v>25</v>
+      </c>
       <c r="R149" t="n">
         <v>0.007162595331923463</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21932,22 +21594,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22209,14 +21861,12 @@
       <c r="O151" t="n">
         <v>23</v>
       </c>
+      <c r="P151" t="n">
+        <v>23</v>
+      </c>
       <c r="R151" t="n">
         <v>0.006589587705369587</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22229,22 +21879,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -24348,14 +23988,12 @@
       <c r="O166" t="n">
         <v>18</v>
       </c>
+      <c r="P166" t="n">
+        <v>18</v>
+      </c>
       <c r="R166" t="n">
         <v>0.005157068638984894</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24368,22 +24006,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24645,14 +24273,12 @@
       <c r="O168" t="n">
         <v>13</v>
       </c>
+      <c r="P168" t="n">
+        <v>13</v>
+      </c>
       <c r="R168" t="n">
         <v>0.003724549572600201</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24665,22 +24291,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24942,14 +24558,12 @@
       <c r="O170" t="n">
         <v>14</v>
       </c>
+      <c r="P170" t="n">
+        <v>14</v>
+      </c>
       <c r="R170" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24962,22 +24576,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -25239,14 +24843,12 @@
       <c r="O172" t="n">
         <v>20</v>
       </c>
+      <c r="P172" t="n">
+        <v>20</v>
+      </c>
       <c r="R172" t="n">
         <v>0.00573007626553877</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25259,22 +24861,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -25536,14 +25128,12 @@
       <c r="O174" t="n">
         <v>14</v>
       </c>
+      <c r="P174" t="n">
+        <v>14</v>
+      </c>
       <c r="R174" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25556,22 +25146,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27390,14 +26970,12 @@
       <c r="O187" t="n">
         <v>6</v>
       </c>
+      <c r="P187" t="n">
+        <v>6</v>
+      </c>
       <c r="R187" t="n">
         <v>0.001719022879661631</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27410,22 +26988,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -27687,14 +27255,12 @@
       <c r="O189" t="n">
         <v>12</v>
       </c>
+      <c r="P189" t="n">
+        <v>12</v>
+      </c>
       <c r="R189" t="n">
         <v>0.003438045759323263</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27707,22 +27273,12 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27984,14 +27540,12 @@
       <c r="O191" t="n">
         <v>16</v>
       </c>
+      <c r="P191" t="n">
+        <v>16</v>
+      </c>
       <c r="R191" t="n">
         <v>0.004584061012431017</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28004,22 +27558,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -28281,14 +27825,12 @@
       <c r="O193" t="n">
         <v>16</v>
       </c>
+      <c r="P193" t="n">
+        <v>16</v>
+      </c>
       <c r="R193" t="n">
         <v>0.004584061012431017</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28301,22 +27843,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -28717,13 +28249,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
@@ -28866,14 +28398,12 @@
       <c r="O197" t="n">
         <v>21</v>
       </c>
+      <c r="P197" t="n">
+        <v>21</v>
+      </c>
       <c r="R197" t="n">
         <v>0.006016580078815709</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28886,22 +28416,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -29163,14 +28683,12 @@
       <c r="O199" t="n">
         <v>9</v>
       </c>
+      <c r="P199" t="n">
+        <v>9</v>
+      </c>
       <c r="R199" t="n">
         <v>0.002578534319492447</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29183,23 +28701,13 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
       </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV199" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -29236,6 +28744,291 @@
         </is>
       </c>
       <c r="BC199" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>20</v>
+      </c>
+      <c r="O201" t="n">
+        <v>20</v>
+      </c>
+      <c r="P201" t="n">
+        <v>20</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.00573007626553877</v>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29274,7 +29067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29150,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -29367,7 +29160,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -29419,7 +29212,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>893</v>
+        <v>914</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -28066,12 +28066,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -28111,11 +28111,11 @@
         <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
@@ -28135,7 +28135,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_140</t>
+          <t>SER_AU_HEPATITIS_B_NEW</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -28143,42 +28143,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28210,12 +28210,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -28255,11 +28255,11 @@
         <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_202_MONTHLY</t>
+          <t>SER_FI_THL_TTR_140</t>
         </is>
       </c>
       <c r="AT196" t="n">
@@ -28287,42 +28287,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28354,12 +28354,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -28384,7 +28384,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -28393,25 +28393,27 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>21</v>
-      </c>
-      <c r="P197" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R197" t="n">
-        <v>0.006016580078815709</v>
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
@@ -28419,48 +28421,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS197" t="inlineStr"/>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_202_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28492,12 +28498,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -28522,7 +28528,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -28531,21 +28537,16 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="P198" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="R198" t="n">
-        <v>0.05079797265291142</v>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
-        </is>
+        <v>0.006016580078815709</v>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
@@ -28554,7 +28555,7 @@
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
@@ -28562,52 +28563,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
-        </is>
-      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28639,12 +28636,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -28669,7 +28666,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -28678,16 +28675,21 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P199" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R199" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
@@ -28696,7 +28698,7 @@
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
@@ -28704,48 +28706,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS199" t="inlineStr"/>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
       <c r="AT199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28777,12 +28783,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -28807,7 +28813,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -28816,21 +28822,16 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P200" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
-        </is>
+        <v>0.002578534319492447</v>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
@@ -28839,7 +28840,7 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
@@ -28847,52 +28848,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
-        </is>
-      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28924,111 +28921,258 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>急性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_B</t>
+        </is>
+      </c>
+      <c r="AT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA201" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>acute-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G202" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>D068</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>Acute hepatitis B</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D068</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
         <is>
           <t>急性乙型肝炎</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N201" t="n">
+      <c r="N202" t="n">
         <v>20</v>
       </c>
-      <c r="O201" t="n">
+      <c r="O202" t="n">
         <v>20</v>
       </c>
-      <c r="P201" t="n">
+      <c r="P202" t="n">
         <v>20</v>
       </c>
-      <c r="R201" t="n">
+      <c r="R202" t="n">
         <v>0.00573007626553877</v>
       </c>
-      <c r="AA201" t="inlineStr">
+      <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AO201" t="inlineStr">
+      <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP201" t="inlineStr">
+      <c r="AP202" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS201" t="inlineStr"/>
-      <c r="AT201" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV201" t="inlineStr">
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV202" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW201" t="inlineStr">
+      <c r="AW202" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX201" t="inlineStr">
+      <c r="AX202" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY201" t="inlineStr">
+      <c r="AY202" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ201" t="inlineStr">
+      <c r="AZ202" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA201" t="inlineStr">
+      <c r="BA202" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB201" t="inlineStr">
+      <c r="BB202" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC201" t="inlineStr">
+      <c r="BC202" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29150,7 +29294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -29160,7 +29304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -29212,7 +29356,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d068/2026-2029.xlsx
+++ b/diseases/d068/2026-2029.xlsx
@@ -55180,13 +55180,13 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R302" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
@@ -55339,10 +55339,10 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U303" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="16">
